--- a/research/traditional_assets/database/data/gibraltar/gibraltar_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/gibraltar/gibraltar_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-1.21</v>
+        <v>-1.41</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,31 +612,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="V2">
-        <v>0.2512562814070352</v>
+        <v>0.2491379310344828</v>
       </c>
       <c r="W2">
-        <v>-1.54140127388535</v>
+        <v>-0.2117117117117117</v>
       </c>
       <c r="X2">
-        <v>0.0628548689397897</v>
+        <v>0.12069905892395</v>
       </c>
       <c r="Y2">
-        <v>-1.60425614282514</v>
+        <v>-0.3324107706356617</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-3.080459770114943</v>
+        <v>-0.8012048192771084</v>
       </c>
       <c r="AB2">
-        <v>0.0628548689397897</v>
+        <v>0.12069905892395</v>
       </c>
       <c r="AC2">
-        <v>-3.143314639054732</v>
+        <v>-0.9219038782010583</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-5</v>
+        <v>-2.89</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,22 +657,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.3355704697986577</v>
+        <v>-0.3318025258323766</v>
       </c>
       <c r="AK2">
-        <v>-3.012048192771084</v>
+        <v>-1.402912621359223</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>-0</v>
-      </c>
-      <c r="AP2">
-        <v>3.816793893129771</v>
+        <v>-0.041</v>
+      </c>
+      <c r="AQ2">
+        <v>32.4390243902439</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +689,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.21</v>
+        <v>-1.41</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,31 +713,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="V3">
-        <v>0.2512562814070352</v>
+        <v>0.2491379310344828</v>
       </c>
       <c r="W3">
-        <v>-1.54140127388535</v>
+        <v>-0.2117117117117117</v>
       </c>
       <c r="X3">
-        <v>0.0628548689397897</v>
+        <v>0.12069905892395</v>
       </c>
       <c r="Y3">
-        <v>-1.60425614282514</v>
+        <v>-0.3324107706356617</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-3.080459770114943</v>
+        <v>-0.8012048192771084</v>
       </c>
       <c r="AB3">
-        <v>0.0628548689397897</v>
+        <v>0.12069905892395</v>
       </c>
       <c r="AC3">
-        <v>-3.143314639054732</v>
+        <v>-0.9219038782010583</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -752,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5</v>
+        <v>-2.89</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -761,22 +758,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3355704697986577</v>
+        <v>-0.3318025258323766</v>
       </c>
       <c r="AK3">
-        <v>-3.012048192771084</v>
+        <v>-1.402912621359223</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AP3">
-        <v>3.816793893129771</v>
+        <v>-0.041</v>
+      </c>
+      <c r="AQ3">
+        <v>32.4390243902439</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/gibraltar/gibraltar_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/gibraltar/gibraltar_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-1.41</v>
+        <v>-1.81</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,31 +612,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.89</v>
+        <v>0.544</v>
       </c>
       <c r="V2">
-        <v>0.2491379310344828</v>
+        <v>0.1219730941704036</v>
       </c>
       <c r="W2">
-        <v>-0.2117117117117117</v>
+        <v>-0.3656565656565657</v>
       </c>
       <c r="X2">
-        <v>0.12069905892395</v>
+        <v>0.1473649063823435</v>
       </c>
       <c r="Y2">
-        <v>-0.3324107706356617</v>
+        <v>-0.5130214720389092</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.8012048192771084</v>
+        <v>-0.8398058252427184</v>
       </c>
       <c r="AB2">
-        <v>0.12069905892395</v>
+        <v>0.1473649063823435</v>
       </c>
       <c r="AC2">
-        <v>-0.9219038782010583</v>
+        <v>-0.987170731625062</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2.89</v>
+        <v>-0.544</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,19 +657,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.3318025258323766</v>
+        <v>-0.1389172625127681</v>
       </c>
       <c r="AK2">
-        <v>-1.402912621359223</v>
+        <v>-0.08894702419882278</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.041</v>
-      </c>
-      <c r="AQ2">
-        <v>32.4390243902439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +686,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.41</v>
+        <v>-1.81</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -713,31 +710,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.89</v>
+        <v>0.544</v>
       </c>
       <c r="V3">
-        <v>0.2491379310344828</v>
+        <v>0.1219730941704036</v>
       </c>
       <c r="W3">
-        <v>-0.2117117117117117</v>
+        <v>-0.3656565656565657</v>
       </c>
       <c r="X3">
-        <v>0.12069905892395</v>
+        <v>0.1473649063823435</v>
       </c>
       <c r="Y3">
-        <v>-0.3324107706356617</v>
+        <v>-0.5130214720389092</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.8012048192771084</v>
+        <v>-0.8398058252427184</v>
       </c>
       <c r="AB3">
-        <v>0.12069905892395</v>
+        <v>0.1473649063823435</v>
       </c>
       <c r="AC3">
-        <v>-0.9219038782010583</v>
+        <v>-0.987170731625062</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -749,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.89</v>
+        <v>-0.544</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -758,19 +755,16 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3318025258323766</v>
+        <v>-0.1389172625127681</v>
       </c>
       <c r="AK3">
-        <v>-1.402912621359223</v>
+        <v>-0.08894702419882278</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.041</v>
-      </c>
-      <c r="AQ3">
-        <v>32.4390243902439</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
